--- a/exports/trend_1d/TVSMOTOR_full_report.xlsx
+++ b/exports/trend_1d/TVSMOTOR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:U62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>13.37</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42058</v>
+        <v>42059</v>
       </c>
       <c r="H2" t="n">
-        <v>289.45</v>
+        <v>269.55</v>
       </c>
       <c r="I2" t="n">
         <v>281.809</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>-8.42</v>
+        <v>-14.71</v>
       </c>
       <c r="L2" t="n">
-        <v>11.28</v>
+        <v>15.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.36</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.22</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H3" t="n">
-        <v>239.45</v>
+        <v>245.05</v>
       </c>
       <c r="I3" t="n">
         <v>243.7280196436373</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K3" t="n">
-        <v>11.17</v>
+        <v>9.09</v>
       </c>
       <c r="L3" t="n">
         <v>10.33</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.08</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42209</v>
+        <v>42212</v>
       </c>
       <c r="H4" t="n">
-        <v>251.55</v>
+        <v>241.1</v>
       </c>
       <c r="I4" t="n">
         <v>243.1352269169323</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K4" t="n">
-        <v>2.65</v>
+        <v>-1.61</v>
       </c>
       <c r="L4" t="n">
         <v>4.1</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>14.1</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42283</v>
+        <v>42284</v>
       </c>
       <c r="H5" t="n">
-        <v>230.25</v>
+        <v>241.4</v>
       </c>
       <c r="I5" t="n">
         <v>240.0938387802831</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>-0.12</v>
       </c>
       <c r="L5" t="n">
         <v>4.31</v>
@@ -726,7 +785,7 @@
         <v>1.6</v>
       </c>
       <c r="N5" t="n">
-        <v>3.71</v>
+        <v>4.84</v>
       </c>
       <c r="O5" t="n">
         <v>-4.15</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42345</v>
+        <v>42346</v>
       </c>
       <c r="H6" t="n">
-        <v>281.75</v>
+        <v>275.14</v>
       </c>
       <c r="I6" t="n">
         <v>281.4782995304989</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K6" t="n">
-        <v>16.71</v>
+        <v>13.98</v>
       </c>
       <c r="L6" t="n">
         <v>5.55</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>11.42</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42447</v>
+        <v>42450</v>
       </c>
       <c r="H7" t="n">
-        <v>287.4</v>
+        <v>305.3</v>
       </c>
       <c r="I7" t="n">
         <v>295.8023610862433</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.46</v>
+        <v>-10.96</v>
       </c>
       <c r="L7" t="n">
-        <v>10.03</v>
+        <v>11.58</v>
       </c>
       <c r="M7" t="n">
         <v>2.11</v>
       </c>
       <c r="N7" t="n">
-        <v>5.84</v>
+        <v>6.23</v>
       </c>
       <c r="O7" t="n">
         <v>-2.35</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>11.43</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42492</v>
+        <v>42493</v>
       </c>
       <c r="H8" t="n">
-        <v>318.95</v>
+        <v>287.45</v>
       </c>
       <c r="I8" t="n">
         <v>310.6717789398983</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K8" t="n">
-        <v>4.47</v>
+        <v>-5.85</v>
       </c>
       <c r="L8" t="n">
-        <v>5.99</v>
+        <v>8.6</v>
       </c>
       <c r="M8" t="n">
         <v>1.19</v>
       </c>
       <c r="N8" t="n">
-        <v>3.11</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="O8" t="n">
         <v>6.23</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>19</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42550</v>
+        <v>42551</v>
       </c>
       <c r="H9" t="n">
-        <v>300.3</v>
+        <v>309.5</v>
       </c>
       <c r="I9" t="n">
         <v>308.5306514846719</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.47</v>
+        <v>-7.67</v>
       </c>
       <c r="L9" t="n">
         <v>13.2</v>
@@ -954,7 +1061,7 @@
         <v>2.53</v>
       </c>
       <c r="N9" t="n">
-        <v>2.67</v>
+        <v>3.06</v>
       </c>
       <c r="O9" t="n">
         <v>-9.880000000000001</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>7.91</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42576</v>
+        <v>42577</v>
       </c>
       <c r="H10" t="n">
-        <v>300.9</v>
+        <v>291.25</v>
       </c>
       <c r="I10" t="n">
         <v>292.3603666368042</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.78</v>
+        <v>-5.9</v>
       </c>
       <c r="L10" t="n">
-        <v>5.12</v>
+        <v>6.67</v>
       </c>
       <c r="M10" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>3.21</v>
       </c>
       <c r="O10" t="n">
         <v>3.06</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>12.32</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42611</v>
+        <v>42612</v>
       </c>
       <c r="H11" t="n">
-        <v>311.55</v>
+        <v>326.05</v>
       </c>
       <c r="I11" t="n">
         <v>313.3342455431059</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K11" t="n">
-        <v>-6.97</v>
+        <v>-11.95</v>
       </c>
       <c r="L11" t="n">
-        <v>8.84</v>
+        <v>12.67</v>
       </c>
       <c r="M11" t="n">
         <v>1.68</v>
       </c>
       <c r="N11" t="n">
-        <v>4.51</v>
+        <v>4.65</v>
       </c>
       <c r="O11" t="n">
         <v>-3.21</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42684</v>
+        <v>42685</v>
       </c>
       <c r="H12" t="n">
-        <v>379.15</v>
+        <v>361.8</v>
       </c>
       <c r="I12" t="n">
         <v>372.1271929579235</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K12" t="n">
-        <v>16.29</v>
+        <v>10.96</v>
       </c>
       <c r="L12" t="n">
         <v>4.92</v>
@@ -1125,7 +1268,7 @@
         <v>9.32</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>4.58</v>
       </c>
       <c r="O12" t="n">
         <v>4.65</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>13.49</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42739</v>
+        <v>42740</v>
       </c>
       <c r="H13" t="n">
-        <v>375.25</v>
+        <v>384.8</v>
       </c>
       <c r="I13" t="n">
         <v>380.9395525023222</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.72</v>
+        <v>-6.36</v>
       </c>
       <c r="L13" t="n">
-        <v>7.08</v>
+        <v>7.71</v>
       </c>
       <c r="M13" t="n">
         <v>1.48</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H14" t="n">
-        <v>580.75</v>
+        <v>536.8</v>
       </c>
       <c r="I14" t="n">
         <v>565.8298943045704</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K14" t="n">
-        <v>50.92</v>
+        <v>39.5</v>
       </c>
       <c r="L14" t="n">
         <v>2.42</v>
@@ -1239,7 +1406,7 @@
         <v>2.15</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>7.57</v>
       </c>
       <c r="O14" t="n">
         <v>2.54</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>12.29</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42971</v>
+        <v>42975</v>
       </c>
       <c r="H15" t="n">
-        <v>595.15</v>
+        <v>604.65</v>
       </c>
       <c r="I15" t="n">
         <v>602.7784238467713</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.87</v>
+        <v>-12.64</v>
       </c>
       <c r="L15" t="n">
-        <v>11.11</v>
+        <v>13.17</v>
       </c>
       <c r="M15" t="n">
         <v>1.16</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.380000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H16" t="n">
-        <v>740.45</v>
+        <v>722.55</v>
       </c>
       <c r="I16" t="n">
         <v>732.5248809151459</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K16" t="n">
-        <v>22.46</v>
+        <v>19.5</v>
       </c>
       <c r="L16" t="n">
         <v>2.02</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>7.5</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H17" t="n">
-        <v>619.3</v>
+        <v>660.45</v>
       </c>
       <c r="I17" t="n">
         <v>654.0559999413227</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K17" t="n">
-        <v>14.29</v>
+        <v>8.59</v>
       </c>
       <c r="L17" t="n">
         <v>2.47</v>
@@ -1410,7 +1613,7 @@
         <v>1.37</v>
       </c>
       <c r="N17" t="n">
-        <v>5.77</v>
+        <v>6.64</v>
       </c>
       <c r="O17" t="n">
         <v>-2.42</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>13.89</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43223</v>
+        <v>43224</v>
       </c>
       <c r="H18" t="n">
-        <v>638.65</v>
+        <v>616.05</v>
       </c>
       <c r="I18" t="n">
         <v>618.710008819892</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.3</v>
+        <v>-6.72</v>
       </c>
       <c r="L18" t="n">
-        <v>6.12</v>
+        <v>7.94</v>
       </c>
       <c r="M18" t="n">
         <v>1.18</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.93</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43339</v>
+        <v>43340</v>
       </c>
       <c r="H19" t="n">
-        <v>563.25</v>
+        <v>569.5</v>
       </c>
       <c r="I19" t="n">
         <v>563.4273346343602</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K19" t="n">
-        <v>8.57</v>
+        <v>7.56</v>
       </c>
       <c r="L19" t="n">
         <v>4.53</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43374</v>
+        <v>43376</v>
       </c>
       <c r="H20" t="n">
-        <v>561.35</v>
+        <v>538.45</v>
       </c>
       <c r="I20" t="n">
         <v>550.2817549545804</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.43</v>
+        <v>-5.45</v>
       </c>
       <c r="L20" t="n">
         <v>7.64</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>16.13</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43448</v>
+        <v>43451</v>
       </c>
       <c r="H21" t="n">
-        <v>570</v>
+        <v>575.1</v>
       </c>
       <c r="I21" t="n">
         <v>573.8420865786068</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.86</v>
+        <v>-6.81</v>
       </c>
       <c r="L21" t="n">
         <v>7.71</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43487</v>
+        <v>43488</v>
       </c>
       <c r="H22" t="n">
-        <v>554.2</v>
+        <v>531.55</v>
       </c>
       <c r="I22" t="n">
         <v>531.6273917670028</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.63</v>
+        <v>-7.57</v>
       </c>
       <c r="L22" t="n">
         <v>9.390000000000001</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>11.07</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43532</v>
+        <v>43535</v>
       </c>
       <c r="H23" t="n">
-        <v>487</v>
+        <v>505.85</v>
       </c>
       <c r="I23" t="n">
         <v>503.4930583860616</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K23" t="n">
-        <v>8.380000000000001</v>
+        <v>4.83</v>
       </c>
       <c r="L23" t="n">
         <v>4.21</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.1</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H24" t="n">
-        <v>492.25</v>
+        <v>478.95</v>
       </c>
       <c r="I24" t="n">
         <v>483.6217641347874</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.69</v>
+        <v>-5.32</v>
       </c>
       <c r="L24" t="n">
-        <v>9.6</v>
+        <v>10.65</v>
       </c>
       <c r="M24" t="n">
-        <v>0.57</v>
+        <v>5.74</v>
       </c>
       <c r="N24" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="O24" t="n">
         <v>3.87</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>7.78</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H25" t="n">
-        <v>389</v>
+        <v>402.95</v>
       </c>
       <c r="I25" t="n">
         <v>398.2626131128676</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K25" t="n">
-        <v>18.78</v>
+        <v>15.87</v>
       </c>
       <c r="L25" t="n">
         <v>6.85</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>14.33</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43871</v>
+        <v>43872</v>
       </c>
       <c r="H26" t="n">
-        <v>456.2</v>
+        <v>451</v>
       </c>
       <c r="I26" t="n">
         <v>451.4201062153659</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K26" t="n">
-        <v>13.22</v>
+        <v>11.92</v>
       </c>
       <c r="L26" t="n">
         <v>8.56</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>11.51</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43980</v>
+        <v>43983</v>
       </c>
       <c r="H27" t="n">
-        <v>335.9</v>
+        <v>352</v>
       </c>
       <c r="I27" t="n">
         <v>348.8846642607213</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
-        <v>25.52</v>
+        <v>21.95</v>
       </c>
       <c r="L27" t="n">
         <v>2.36</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.7</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44127</v>
+        <v>44130</v>
       </c>
       <c r="H28" t="n">
-        <v>444.65</v>
+        <v>429.7</v>
       </c>
       <c r="I28" t="n">
         <v>430.5559161752294</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K28" t="n">
-        <v>26.32</v>
+        <v>22.07</v>
       </c>
       <c r="L28" t="n">
         <v>12.73</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>12.2</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44138</v>
+        <v>44139</v>
       </c>
       <c r="H29" t="n">
-        <v>465.7</v>
+        <v>470.95</v>
       </c>
       <c r="I29" t="n">
         <v>467.4771584648709</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.380000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="L29" t="n">
-        <v>9.56</v>
+        <v>10.08</v>
       </c>
       <c r="M29" t="n">
         <v>0.97</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>11.02</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44183</v>
+        <v>44186</v>
       </c>
       <c r="H30" t="n">
-        <v>489.1</v>
+        <v>464.9</v>
       </c>
       <c r="I30" t="n">
         <v>468.8350663799021</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K30" t="n">
-        <v>3.85</v>
+        <v>-1.28</v>
       </c>
       <c r="L30" t="n">
-        <v>1.69</v>
+        <v>3.73</v>
       </c>
       <c r="M30" t="n">
         <v>0.62</v>
       </c>
       <c r="N30" t="n">
-        <v>2.79</v>
+        <v>4.95</v>
       </c>
       <c r="O30" t="n">
         <v>1.13</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44203</v>
+        <v>44204</v>
       </c>
       <c r="H31" t="n">
-        <v>499.3</v>
+        <v>513.35</v>
       </c>
       <c r="I31" t="n">
         <v>511.3601744878083</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K31" t="n">
-        <v>-7.4</v>
+        <v>-10.42</v>
       </c>
       <c r="L31" t="n">
-        <v>8.93</v>
+        <v>11.21</v>
       </c>
       <c r="M31" t="n">
         <v>1.46</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44272</v>
+        <v>44273</v>
       </c>
       <c r="H32" t="n">
-        <v>577.7</v>
+        <v>571</v>
       </c>
       <c r="I32" t="n">
         <v>574.4202116949208</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K32" t="n">
-        <v>12.54</v>
+        <v>11.23</v>
       </c>
       <c r="L32" t="n">
         <v>4.82</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.1</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44313</v>
+        <v>44314</v>
       </c>
       <c r="H33" t="n">
-        <v>566.3</v>
+        <v>645.8</v>
       </c>
       <c r="I33" t="n">
         <v>585.9447020147703</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>0.82</v>
+        <v>-13.1</v>
       </c>
       <c r="L33" t="n">
-        <v>3.86</v>
+        <v>16.29</v>
       </c>
       <c r="M33" t="n">
-        <v>1.32</v>
+        <v>6.83</v>
       </c>
       <c r="N33" t="n">
-        <v>3.73</v>
+        <v>14.04</v>
       </c>
       <c r="O33" t="n">
         <v>-1.16</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>14.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H34" t="n">
-        <v>601.4</v>
+        <v>583.05</v>
       </c>
       <c r="I34" t="n">
         <v>589.6731067424612</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.88</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>8.19</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M34" t="n">
         <v>2.04</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44445</v>
+        <v>44446</v>
       </c>
       <c r="H35" t="n">
-        <v>546.45</v>
+        <v>553.8</v>
       </c>
       <c r="I35" t="n">
         <v>552.6913181283453</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K35" t="n">
-        <v>6.28</v>
+        <v>5.02</v>
       </c>
       <c r="L35" t="n">
         <v>3.76</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>8.73</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H36" t="n">
-        <v>701.5</v>
+        <v>676.8</v>
       </c>
       <c r="I36" t="n">
         <v>679.1560155989404</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" t="n">
-        <v>26.67</v>
+        <v>22.21</v>
       </c>
       <c r="L36" t="n">
         <v>6.1</v>
@@ -2493,7 +2924,7 @@
         <v>1.93</v>
       </c>
       <c r="N36" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="O36" t="n">
         <v>1.35</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>12.79</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44601</v>
+        <v>44602</v>
       </c>
       <c r="H37" t="n">
-        <v>659.85</v>
+        <v>668.45</v>
       </c>
       <c r="I37" t="n">
         <v>662.7974436979326</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K37" t="n">
-        <v>2.5</v>
+        <v>1.23</v>
       </c>
       <c r="L37" t="n">
         <v>4.73</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>9.92</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44620</v>
+        <v>44622</v>
       </c>
       <c r="H38" t="n">
-        <v>617.6</v>
+        <v>597.95</v>
       </c>
       <c r="I38" t="n">
         <v>602.1169433879921</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.61</v>
+        <v>-10.55</v>
       </c>
       <c r="L38" t="n">
-        <v>8.74</v>
+        <v>10.84</v>
       </c>
       <c r="M38" t="n">
         <v>2.79</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>12.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44635</v>
+        <v>44636</v>
       </c>
       <c r="H39" t="n">
-        <v>594.8</v>
+        <v>609.7</v>
       </c>
       <c r="I39" t="n">
         <v>605.5234013099443</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K39" t="n">
-        <v>0.53</v>
+        <v>-1.97</v>
       </c>
       <c r="L39" t="n">
         <v>2.33</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>11.88</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H40" t="n">
-        <v>649.05</v>
+        <v>627.5</v>
       </c>
       <c r="I40" t="n">
         <v>628.6473319810738</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K40" t="n">
-        <v>6.45</v>
+        <v>2.92</v>
       </c>
       <c r="L40" t="n">
         <v>1.66</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>12.04</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44697</v>
+        <v>44698</v>
       </c>
       <c r="H41" t="n">
-        <v>653.5</v>
+        <v>676.15</v>
       </c>
       <c r="I41" t="n">
         <v>667.8470186153721</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.14</v>
+        <v>-7.75</v>
       </c>
       <c r="L41" t="n">
-        <v>4.47</v>
+        <v>8.73</v>
       </c>
       <c r="M41" t="n">
         <v>1.29</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.71</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44883</v>
+        <v>44886</v>
       </c>
       <c r="H42" t="n">
-        <v>1081.85</v>
+        <v>1048.45</v>
       </c>
       <c r="I42" t="n">
         <v>1060.118348746138</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K42" t="n">
-        <v>60</v>
+        <v>55.06</v>
       </c>
       <c r="L42" t="n">
         <v>3.34</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.88</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44923</v>
+        <v>44924</v>
       </c>
       <c r="H43" t="n">
-        <v>1082.7</v>
+        <v>1101</v>
       </c>
       <c r="I43" t="n">
         <v>1090.798662620276</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.27</v>
+        <v>-5.01</v>
       </c>
       <c r="L43" t="n">
-        <v>3.52</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M43" t="n">
         <v>1.02</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>8.66</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44937</v>
+        <v>44938</v>
       </c>
       <c r="H44" t="n">
-        <v>1014.65</v>
+        <v>1005.55</v>
       </c>
       <c r="I44" t="n">
         <v>1005.635149949818</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K44" t="n">
-        <v>-7.84</v>
+        <v>-8.67</v>
       </c>
       <c r="L44" t="n">
-        <v>8.27</v>
+        <v>9.06</v>
       </c>
       <c r="M44" t="n">
         <v>0.44</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.42</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44966</v>
+        <v>44967</v>
       </c>
       <c r="H45" t="n">
-        <v>1049.8</v>
+        <v>1075.35</v>
       </c>
       <c r="I45" t="n">
         <v>1058.305683061332</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K45" t="n">
-        <v>-4.4</v>
+        <v>-6.94</v>
       </c>
       <c r="L45" t="n">
-        <v>7.13</v>
+        <v>8.1</v>
       </c>
       <c r="M45" t="n">
         <v>1.13</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>10.16</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45365</v>
+        <v>45366</v>
       </c>
       <c r="H46" t="n">
-        <v>2149.8</v>
+        <v>2066.45</v>
       </c>
       <c r="I46" t="n">
         <v>2097.476479909354</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K46" t="n">
-        <v>99.92</v>
+        <v>92.17</v>
       </c>
       <c r="L46" t="n">
         <v>6.54</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>271</v>
+        <v>272</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>14</v>
+      </c>
+      <c r="U46" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.53</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45425</v>
+        <v>45426</v>
       </c>
       <c r="H47" t="n">
-        <v>2068.6</v>
+        <v>2134.8</v>
       </c>
       <c r="I47" t="n">
         <v>2074.463596894299</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1</v>
+        <v>-3.31</v>
       </c>
       <c r="L47" t="n">
         <v>6.22</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.67</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H48" t="n">
-        <v>2838.65</v>
+        <v>2725.6</v>
       </c>
       <c r="I48" t="n">
         <v>2726.01020529371</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K48" t="n">
-        <v>32.97</v>
+        <v>27.67</v>
       </c>
       <c r="L48" t="n">
         <v>3.27</v>
       </c>
       <c r="M48" t="n">
-        <v>2.1</v>
+        <v>2.74</v>
       </c>
       <c r="N48" t="n">
-        <v>3.72</v>
+        <v>3.98</v>
       </c>
       <c r="O48" t="n">
         <v>3.2</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>98</v>
+        <v>99</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>6</v>
+      </c>
+      <c r="U48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="H49" t="n">
-        <v>2335.8</v>
+        <v>2464.75</v>
       </c>
       <c r="I49" t="n">
         <v>2431.294357851755</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K49" t="n">
-        <v>14.3</v>
+        <v>9.57</v>
       </c>
       <c r="L49" t="n">
         <v>4.49</v>
@@ -3234,7 +3821,7 @@
         <v>2.42</v>
       </c>
       <c r="N49" t="n">
-        <v>4.68</v>
+        <v>5.52</v>
       </c>
       <c r="O49" t="n">
         <v>-3.98</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>10.96</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45702</v>
+        <v>45705</v>
       </c>
       <c r="H50" t="n">
-        <v>2401.4</v>
+        <v>2365.7</v>
       </c>
       <c r="I50" t="n">
         <v>2380.774655802015</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.57</v>
+        <v>-4.02</v>
       </c>
       <c r="L50" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>11.35</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45748</v>
+        <v>45749</v>
       </c>
       <c r="H51" t="n">
-        <v>2440.85</v>
+        <v>2496.1</v>
       </c>
       <c r="I51" t="n">
         <v>2495.6274493399</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.18</v>
+        <v>-5.51</v>
       </c>
       <c r="L51" t="n">
-        <v>4.32</v>
+        <v>6.46</v>
       </c>
       <c r="M51" t="n">
         <v>1.95</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H52" t="n">
-        <v>3473.1</v>
+        <v>3446.8</v>
       </c>
       <c r="I52" t="n">
         <v>3466.947065472209</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K52" t="n">
-        <v>39.14</v>
+        <v>38.09</v>
       </c>
       <c r="L52" t="n">
         <v>11.02</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.21</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="H53" t="n">
-        <v>3531.5</v>
+        <v>3661.8</v>
       </c>
       <c r="I53" t="n">
         <v>3639.361908953277</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.46</v>
+        <v>-6.24</v>
       </c>
       <c r="L53" t="n">
-        <v>3.71</v>
+        <v>6.36</v>
       </c>
       <c r="M53" t="n">
         <v>0.62</v>
       </c>
       <c r="N53" t="n">
-        <v>2.63</v>
+        <v>3.69</v>
       </c>
       <c r="O53" t="n">
         <v>-0.76</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>7.49</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H54" t="n">
-        <v>3701.9</v>
+        <v>3615.7</v>
       </c>
       <c r="I54" t="n">
         <v>3651.817936073815</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K54" t="n">
-        <v>1.1</v>
+        <v>-1.26</v>
       </c>
       <c r="L54" t="n">
         <v>3.24</v>
@@ -3519,7 +4166,7 @@
         <v>0.68</v>
       </c>
       <c r="N54" t="n">
-        <v>1.73</v>
+        <v>2.33</v>
       </c>
       <c r="O54" t="n">
         <v>3.69</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H55" t="n">
-        <v>3762.4</v>
+        <v>3865.1</v>
       </c>
       <c r="I55" t="n">
         <v>3813.088775406929</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.06</v>
+        <v>-6.9</v>
       </c>
       <c r="L55" t="n">
-        <v>5.65</v>
+        <v>7.56</v>
       </c>
       <c r="M55" t="n">
         <v>4.69</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>8.75</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H56" t="n">
-        <v>3784</v>
+        <v>3627.8</v>
       </c>
       <c r="I56" t="n">
         <v>3681.780699970678</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.1</v>
+        <v>-6.14</v>
       </c>
       <c r="L56" t="n">
-        <v>5.69</v>
+        <v>7.31</v>
       </c>
       <c r="M56" t="n">
         <v>2.32</v>
       </c>
       <c r="N56" t="n">
-        <v>2.14</v>
+        <v>4.13</v>
       </c>
       <c r="O56" t="n">
         <v>2.73</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H57" t="n">
-        <v>3701.4</v>
+        <v>3727.1</v>
       </c>
       <c r="I57" t="n">
         <v>3702.801216055407</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.03</v>
+        <v>-2.74</v>
       </c>
       <c r="L57" t="n">
         <v>4.68</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.44</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="H58" t="n">
-        <v>3527.2</v>
+        <v>3460.8</v>
       </c>
       <c r="I58" t="n">
         <v>3462.847763924391</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.36</v>
+        <v>-7.14</v>
       </c>
       <c r="L58" t="n">
         <v>9.640000000000001</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.21</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="H59" t="n">
-        <v>3440.6</v>
+        <v>3569.7</v>
       </c>
       <c r="I59" t="n">
         <v>3560.525812605682</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K59" t="n">
-        <v>0.58</v>
+        <v>-3.15</v>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>4.09</v>
       </c>
       <c r="M59" t="n">
         <v>1.49</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.48</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H60" t="n">
-        <v>4341.3</v>
+        <v>4203</v>
       </c>
       <c r="I60" t="n">
         <v>4223.031914628955</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K60" t="n">
-        <v>21.62</v>
+        <v>17.74</v>
       </c>
       <c r="L60" t="n">
         <v>3.94</v>
@@ -3861,7 +4580,7 @@
         <v>1.26</v>
       </c>
       <c r="N60" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="O60" t="n">
         <v>3.75</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.69</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H61" t="n">
-        <v>4087</v>
+        <v>4239</v>
       </c>
       <c r="I61" t="n">
         <v>4151.120780287594</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K61" t="n">
-        <v>2.76</v>
+        <v>-0.86</v>
       </c>
       <c r="L61" t="n">
         <v>4.9</v>
@@ -3918,7 +4649,7 @@
         <v>0.75</v>
       </c>
       <c r="N61" t="n">
-        <v>2.28</v>
+        <v>3.72</v>
       </c>
       <c r="O61" t="n">
         <v>-3.19</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3978,6 +4721,12 @@
       <c r="Q62" t="n">
         <v>1</v>
       </c>
+      <c r="R62" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8936,7 +9685,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.09999999999999</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="6">
@@ -8946,7 +9695,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="7">
@@ -8956,7 +9705,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8">
@@ -8966,7 +9715,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -8976,7 +9725,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.8</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="10">
@@ -8986,7 +9735,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140.4</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="11">
@@ -8996,7 +9745,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -9006,7 +9755,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -9016,7 +9765,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.3</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="14">
@@ -9026,7 +9775,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7.43</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="15">
@@ -9036,7 +9785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13.42</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="16">
@@ -9046,7 +9795,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.44</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="17">
@@ -9056,7 +9805,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.92</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="18">
@@ -9066,7 +9815,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53.3</v>
+        <v>38.3</v>
       </c>
     </row>
     <row r="19">
@@ -9076,7 +9825,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.06</v>
+        <v>7.08</v>
       </c>
     </row>
     <row r="20">
@@ -9086,7 +9835,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.34</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="21">
@@ -9096,7 +9845,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.2</v>
+        <v>16.29</v>
       </c>
     </row>
     <row r="22">
@@ -9106,7 +9855,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -9116,7 +9865,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -9126,7 +9875,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="25">
@@ -9146,7 +9895,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.31</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="27">
@@ -9156,7 +9905,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.960000000000001</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="28">
@@ -9166,7 +9915,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
